--- a/input/mapping/093.OCB_GOLD_TTDL_FACT_BPM_AP_SLA_LINH.xlsx
+++ b/input/mapping/093.OCB_GOLD_TTDL_FACT_BPM_AP_SLA_LINH.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30410"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anh Hoang Tram\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="182" documentId="13_ncr:1_{B1158EF6-AECF-4F6B-AAD1-01C8F902D40A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF24346B-DDEE-4802-BCA0-DCB0D9925417}"/>
+  <xr:revisionPtr revIDLastSave="183" documentId="13_ncr:1_{B1158EF6-AECF-4F6B-AAD1-01C8F902D40A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC38BC66-4775-423A-9925-1FB31E625313}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1530" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="1" xr2:uid="{13D98049-6EC7-482C-8699-FBF0F790C51A}"/>
+    <workbookView xWindow="-28920" yWindow="-1530" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{13D98049-6EC7-482C-8699-FBF0F790C51A}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="6" r:id="rId1"/>
@@ -554,45 +554,50 @@
   <si>
     <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tcimport;
-CREATE OR REPLACE TABLE FACT_BPM_AP_SLA AS
+INSERT OVERWRITE FACT_BPM_AP_SLA
+(
+    DATE_COB, AP_ID, AP_NBR, VI_TRI, TGIAN_XLY, THOI_DIEM_NHAN, THOI_DIEM_NHAN_CUOI, SLA, PPN_TM,
+    SRC_STM_CODE
+)
 WITH gd_active AS (
     SELECT giao_dich_hashkey AS hk, business_key AS ma_gd
     FROM IDENTIFIER(:cleaned || '.raw_vault.hub_giao_dich')
-    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    WHERE source_event_date &lt;= TO_DATE(:target_date, 'yyyyMMdd')
 ),
 gd_sla AS (
     SELECT giao_dich_hashkey AS hk,
-           max_by(quy_trinh,                  source_event_date) AS quy_trinh,
-           max_by(thoi_gian_xl_vitri_1,       source_event_date) AS thoi_gian_xl_vitri_1,
-           max_by(thoi_gian_xl_vitri_2,       source_event_date) AS thoi_gian_xl_vitri_2,
-           max_by(thoi_gian_xl_vitri_3,       source_event_date) AS thoi_gian_xl_vitri_3,
-           max_by(thoi_gian_xl_vitri_4,       source_event_date) AS thoi_gian_xl_vitri_4,
-           max_by(thoi_gian_xl_vitri_5,       source_event_date) AS thoi_gian_xl_vitri_5,
-           max_by(thoi_gian_xl_vitri_6,       source_event_date) AS thoi_gian_xl_vitri_6,
-           max_by(thoi_gian_xl_vitri_7,       source_event_date) AS thoi_gian_xl_vitri_7,
-           max_by(thoi_diem_nhan_vitri_1,     source_event_date) AS thoi_diem_nhan_vitri_1,
-           max_by(thoi_diem_nhan_vitri_2,     source_event_date) AS thoi_diem_nhan_vitri_2,
-           max_by(thoi_diem_nhan_vitri_3,     source_event_date) AS thoi_diem_nhan_vitri_3,
-           max_by(thoi_diem_nhan_vitri_4,     source_event_date) AS thoi_diem_nhan_vitri_4,
-           max_by(thoi_diem_nhan_vitri_5,     source_event_date) AS thoi_diem_nhan_vitri_5,
-           max_by(thoi_diem_nhan_vitri_6,     source_event_date) AS thoi_diem_nhan_vitri_6,
-           max_by(thoi_diem_nhan_vitri_7,     source_event_date) AS thoi_diem_nhan_vitri_7,
-           max_by(thoi_diem_nhan_vitri_1_cuoi, source_event_date) AS thoi_diem_nhan_vitri_1_cuoi,
-           max_by(thoi_diem_nhan_vitri_2_cuoi, source_event_date) AS thoi_diem_nhan_vitri_2_cuoi,
-           max_by(thoi_diem_nhan_vitri_3_cuoi, source_event_date) AS thoi_diem_nhan_vitri_3_cuoi,
-           max_by(thoi_diem_nhan_vitri_4_cuoi, source_event_date) AS thoi_diem_nhan_vitri_4_cuoi,
-           max_by(thoi_diem_nhan_vitri_5_cuoi, source_event_date) AS thoi_diem_nhan_vitri_5_cuoi,
-           max_by(thoi_diem_nhan_vitri_6_cuoi, source_event_date) AS thoi_diem_nhan_vitri_6_cuoi,
-           max_by(thoi_diem_nhan_vitri_7_cuoi, source_event_date) AS thoi_diem_nhan_vitri_7_cuoi,
-           max_by(sla_vitri_2,                source_event_date) AS sla_vitri_2,
-           max_by(sla_vitri_3,                source_event_date) AS sla_vitri_3,
-           max_by(sla_vitri_4,                source_event_date) AS sla_vitri_4,
-           max_by(sla_vitri_5,                source_event_date) AS sla_vitri_5,
-           max_by(thoi_gian_den_han,          source_event_date) AS thoi_gian_den_han,
-           max_by(sla,                        source_event_date) AS sla
+           quy_trinh,
+           thoi_gian_xl_vitri_1,
+           thoi_gian_xl_vitri_2,
+           thoi_gian_xl_vitri_3,
+           thoi_gian_xl_vitri_4,
+           thoi_gian_xl_vitri_5,
+           thoi_gian_xl_vitri_6,
+           thoi_gian_xl_vitri_7,
+           thoi_diem_nhan_vitri_1,
+           thoi_diem_nhan_vitri_2,
+           thoi_diem_nhan_vitri_3,
+           thoi_diem_nhan_vitri_4,
+           thoi_diem_nhan_vitri_5,
+           thoi_diem_nhan_vitri_6,
+           thoi_diem_nhan_vitri_7,
+           thoi_diem_nhan_vitri_1_cuoi,
+           thoi_diem_nhan_vitri_2_cuoi,
+           thoi_diem_nhan_vitri_3_cuoi,
+           thoi_diem_nhan_vitri_4_cuoi,
+           thoi_diem_nhan_vitri_5_cuoi,
+           thoi_diem_nhan_vitri_6_cuoi,
+           thoi_diem_nhan_vitri_7_cuoi,
+           sla_vitri_2,
+           sla_vitri_3,
+           sla_vitri_4,
+           sla_vitri_5,
+           thoi_gian_den_han,
+           sla
     FROM IDENTIFIER(:cleaned || '.raw_vault.sat_giaodich_sla')
-    WHERE source_event_date = TO_DATE(:DATADT, 'yyyyMMdd')
-    GROUP BY giao_dich_hashkey
+    WHERE source_event_date = TO_DATE(:target_date, 'yyyyMMdd')
+    QUALIFY ROW_NUMBER() OVER (PARTITION BY giao_dich_hashkey
+                               ORDER BY source_event_date DESC) = 1
 ),
 gd_j AS (
     SELECT h.ma_gd,
@@ -649,7 +654,7 @@
     )) t AS x
 )
 SELECT
-    TO_DATE(:DATADT, 'yyyyMMdd')                   AS DATE_COB,
+    TO_DATE(:target_date, 'yyyyMMdd')                   AS DATE_COB,
     CAST(NULL AS BIGINT)                           AS AP_ID,
     CAST(ap.MA_GIAO_DICH AS STRING)                AS AP_NBR,
     CAST(app_sla.vi_tri AS INT)                    AS VI_TRI,
@@ -3002,6 +3007,27 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3020,43 +3046,22 @@
     <xf numFmtId="0" fontId="24" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="15" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="20" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="15" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="49" fontId="20" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="21" fillId="15" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -3429,7 +3434,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.95" customHeight="1">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="72" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="88"/>
@@ -3464,34 +3469,34 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="76" t="s">
+      <c r="C3" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="77" t="s">
+      <c r="D3" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="78" t="s">
+      <c r="E3" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="77" t="s">
+      <c r="F3" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H3" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="80" t="s">
+      <c r="I3" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="77" t="s">
+      <c r="J3" s="70" t="s">
         <v>8</v>
       </c>
       <c r="K3" s="45" t="s">
@@ -3530,10 +3535,10 @@
       <c r="E6" s="88"/>
       <c r="F6" s="88"/>
       <c r="G6" s="88"/>
-      <c r="I6" s="78" t="s">
+      <c r="I6" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="77" t="s">
+      <c r="J6" s="70" t="s">
         <v>8</v>
       </c>
       <c r="K6" s="45" t="s">
@@ -3929,7 +3934,7 @@
     </row>
     <row r="37" spans="1:11" ht="15.95" customHeight="1">
       <c r="A37" s="19"/>
-      <c r="B37" s="81" t="s">
+      <c r="B37" s="69" t="s">
         <v>44</v>
       </c>
       <c r="C37" s="88"/>
@@ -3939,7 +3944,7 @@
     </row>
     <row r="38" spans="1:11" ht="15.95" customHeight="1">
       <c r="A38" s="20"/>
-      <c r="B38" s="81" t="s">
+      <c r="B38" s="69" t="s">
         <v>45</v>
       </c>
       <c r="C38" s="88"/>
@@ -3949,7 +3954,7 @@
     </row>
     <row r="39" spans="1:11" ht="15.95" customHeight="1">
       <c r="A39" s="21"/>
-      <c r="B39" s="81" t="s">
+      <c r="B39" s="69" t="s">
         <v>46</v>
       </c>
       <c r="C39" s="88"/>
@@ -3959,7 +3964,7 @@
     </row>
     <row r="40" spans="1:11" ht="15.95" customHeight="1">
       <c r="A40" s="22"/>
-      <c r="B40" s="81" t="s">
+      <c r="B40" s="69" t="s">
         <v>47</v>
       </c>
       <c r="C40" s="88"/>
@@ -3969,7 +3974,7 @@
     </row>
     <row r="41" spans="1:11" ht="15.95" customHeight="1">
       <c r="A41" s="23"/>
-      <c r="B41" s="81" t="s">
+      <c r="B41" s="69" t="s">
         <v>48</v>
       </c>
       <c r="C41" s="88"/>
@@ -3983,14 +3988,6 @@
     <row r="45" spans="1:11" ht="15"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="I6:I33"/>
-    <mergeCell ref="J6:J33"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B39:F39"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A3:A33"/>
     <mergeCell ref="B3:B33"/>
@@ -4000,6 +3997,14 @@
     <mergeCell ref="F3:F33"/>
     <mergeCell ref="G3:G33"/>
     <mergeCell ref="I3:I4"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="I6:I33"/>
+    <mergeCell ref="J6:J33"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B39:F39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4130,14 +4135,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21.95" customHeight="1">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="76" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="71"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="78"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -4209,14 +4214,14 @@
       <c r="G5"/>
     </row>
     <row r="6" spans="1:7" s="7" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A6" s="72" t="s">
+      <c r="A6" s="79" t="s">
         <v>78</v>
       </c>
-      <c r="B6" s="73"/>
-      <c r="C6" s="73"/>
-      <c r="D6" s="73"/>
-      <c r="E6" s="73"/>
-      <c r="F6" s="74"/>
+      <c r="B6" s="80"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="80"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="81"/>
       <c r="G6"/>
     </row>
     <row r="7" spans="1:7" s="28" customFormat="1" ht="30" customHeight="1">
@@ -4810,24 +4815,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="85" t="s">
         <v>145</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="87"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="86"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="83" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="86"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="84"/>
     </row>
     <row r="3" spans="1:6" ht="15.75">
       <c r="A3" s="48" t="s">
@@ -4990,14 +4995,14 @@
       <c r="F11" s="52"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="84" t="s">
+      <c r="A12" s="83" t="s">
         <v>178</v>
       </c>
-      <c r="B12" s="84"/>
-      <c r="C12" s="84"/>
-      <c r="D12" s="84"/>
-      <c r="E12" s="84"/>
-      <c r="F12" s="86"/>
+      <c r="B12" s="83"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="84"/>
     </row>
     <row r="13" spans="1:6" ht="15.75">
       <c r="A13" s="48" t="s">
@@ -5124,14 +5129,14 @@
       <c r="F19" s="52"/>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="84" t="s">
+      <c r="A20" s="83" t="s">
         <v>196</v>
       </c>
-      <c r="B20" s="84"/>
-      <c r="C20" s="84"/>
-      <c r="D20" s="84"/>
-      <c r="E20" s="84"/>
-      <c r="F20" s="86"/>
+      <c r="B20" s="83"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="84"/>
     </row>
     <row r="21" spans="1:6" ht="15.75">
       <c r="A21" s="48" t="s">
@@ -5240,14 +5245,14 @@
       <c r="F26" s="52"/>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="84" t="s">
+      <c r="A27" s="83" t="s">
         <v>209</v>
       </c>
-      <c r="B27" s="84"/>
-      <c r="C27" s="84"/>
-      <c r="D27" s="84"/>
-      <c r="E27" s="84"/>
-      <c r="F27" s="86"/>
+      <c r="B27" s="83"/>
+      <c r="C27" s="83"/>
+      <c r="D27" s="83"/>
+      <c r="E27" s="83"/>
+      <c r="F27" s="84"/>
     </row>
     <row r="28" spans="1:6" ht="15.75">
       <c r="A28" s="48" t="s">
@@ -5410,14 +5415,14 @@
       <c r="F36" s="52"/>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="84" t="s">
+      <c r="A37" s="83" t="s">
         <v>230</v>
       </c>
-      <c r="B37" s="84"/>
-      <c r="C37" s="84"/>
-      <c r="D37" s="84"/>
-      <c r="E37" s="84"/>
-      <c r="F37" s="86"/>
+      <c r="B37" s="83"/>
+      <c r="C37" s="83"/>
+      <c r="D37" s="83"/>
+      <c r="E37" s="83"/>
+      <c r="F37" s="84"/>
     </row>
     <row r="38" spans="1:6" ht="15.75">
       <c r="A38" s="48" t="s">
@@ -5498,24 +5503,24 @@
       <c r="F42" s="52"/>
     </row>
     <row r="43" spans="1:6" ht="18.75">
-      <c r="A43" s="83" t="s">
+      <c r="A43" s="85" t="s">
         <v>239</v>
       </c>
-      <c r="B43" s="83"/>
-      <c r="C43" s="83"/>
-      <c r="D43" s="83"/>
-      <c r="E43" s="83"/>
-      <c r="F43" s="83"/>
+      <c r="B43" s="85"/>
+      <c r="C43" s="85"/>
+      <c r="D43" s="85"/>
+      <c r="E43" s="85"/>
+      <c r="F43" s="85"/>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="84" t="s">
+      <c r="A44" s="83" t="s">
         <v>146</v>
       </c>
-      <c r="B44" s="84"/>
-      <c r="C44" s="84"/>
-      <c r="D44" s="84"/>
-      <c r="E44" s="84"/>
-      <c r="F44" s="84"/>
+      <c r="B44" s="83"/>
+      <c r="C44" s="83"/>
+      <c r="D44" s="83"/>
+      <c r="E44" s="83"/>
+      <c r="F44" s="83"/>
     </row>
     <row r="45" spans="1:6" ht="15.75">
       <c r="A45" s="48" t="s">
@@ -5946,14 +5951,14 @@
       <c r="F66" s="52"/>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="84" t="s">
+      <c r="A67" s="83" t="s">
         <v>178</v>
       </c>
-      <c r="B67" s="84"/>
-      <c r="C67" s="85"/>
-      <c r="D67" s="85"/>
-      <c r="E67" s="84"/>
-      <c r="F67" s="84"/>
+      <c r="B67" s="83"/>
+      <c r="C67" s="87"/>
+      <c r="D67" s="87"/>
+      <c r="E67" s="83"/>
+      <c r="F67" s="83"/>
     </row>
     <row r="68" spans="1:6" ht="15.75">
       <c r="A68" s="48" t="s">
@@ -6376,14 +6381,14 @@
       </c>
     </row>
     <row r="89" spans="1:6">
-      <c r="A89" s="84" t="s">
+      <c r="A89" s="83" t="s">
         <v>196</v>
       </c>
-      <c r="B89" s="84"/>
-      <c r="C89" s="85"/>
-      <c r="D89" s="85"/>
-      <c r="E89" s="84"/>
-      <c r="F89" s="84"/>
+      <c r="B89" s="83"/>
+      <c r="C89" s="87"/>
+      <c r="D89" s="87"/>
+      <c r="E89" s="83"/>
+      <c r="F89" s="83"/>
     </row>
     <row r="90" spans="1:6" ht="15.75">
       <c r="A90" s="48" t="s">
@@ -6814,14 +6819,14 @@
       <c r="F111" s="52"/>
     </row>
     <row r="112" spans="1:6">
-      <c r="A112" s="84" t="s">
+      <c r="A112" s="83" t="s">
         <v>209</v>
       </c>
-      <c r="B112" s="84"/>
-      <c r="C112" s="85"/>
-      <c r="D112" s="85"/>
-      <c r="E112" s="84"/>
-      <c r="F112" s="84"/>
+      <c r="B112" s="83"/>
+      <c r="C112" s="87"/>
+      <c r="D112" s="87"/>
+      <c r="E112" s="83"/>
+      <c r="F112" s="83"/>
     </row>
     <row r="113" spans="1:6" ht="15.75">
       <c r="A113" s="48" t="s">
@@ -9357,30 +9362,29 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A112:F112"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="A44:F44"/>
-    <mergeCell ref="A67:F67"/>
-    <mergeCell ref="A89:F89"/>
-    <mergeCell ref="A112:F112"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9556,16 +9560,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F4B8465-14DB-4806-94B0-8C9694FAD3CD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{995D4A7A-7E04-473D-A1FF-9C748A109A3A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9573,5 +9578,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{995D4A7A-7E04-473D-A1FF-9C748A109A3A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F4B8465-14DB-4806-94B0-8C9694FAD3CD}"/>
 </file>